--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484282_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484282_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7326</v>
+        <v>5.9824</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4228</v>
+        <v>3.836</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3098</v>
+        <v>2.1464</v>
       </c>
       <c r="G2" t="n">
         <v>2.7495</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>1.784</v>
+        <v>1.0338</v>
       </c>
       <c r="T2" t="n">
-        <v>1.296</v>
+        <v>0.7093</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4879</v>
+        <v>0.3245</v>
       </c>
       <c r="V2" t="n">
         <v>0.8317</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0708</v>
+        <v>4.8627</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3936</v>
+        <v>2.7326</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6772</v>
+        <v>2.1301</v>
       </c>
       <c r="G3" t="n">
-        <v>2.0399</v>
+        <v>3.3607</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3346</v>
+        <v>2.5654</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.2947</v>
+        <v>0.7953</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5946</v>
+        <v>3.1811</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2144</v>
+        <v>3.1939</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6198</v>
+        <v>-0.0128</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5546</v>
+        <v>0.1796</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1203</v>
+        <v>-0.6284999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6749000000000001</v>
+        <v>0.8081</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
         <v>1.7581</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0346</v>
+        <v>0.2015</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0522</v>
+        <v>0.0091</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0868</v>
+        <v>0.1924</v>
       </c>
       <c r="V3" t="n">
-        <v>2.2149</v>
+        <v>1.4959</v>
       </c>
       <c r="W3" t="n">
-        <v>1.8279</v>
+        <v>1.4959</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3869</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7046</v>
+        <v>4.6785</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2477</v>
+        <v>3.1102</v>
       </c>
       <c r="F4" t="n">
-        <v>2.4569</v>
+        <v>1.5683</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3607</v>
+        <v>2.0399</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5654</v>
+        <v>3.3346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7953</v>
+        <v>-1.2947</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1811</v>
+        <v>2.5946</v>
       </c>
       <c r="K4" t="n">
-        <v>3.1939</v>
+        <v>3.2144</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0128</v>
+        <v>-0.6198</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1796</v>
+        <v>-0.5546</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6284999999999999</v>
+        <v>0.1203</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8081</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0434</v>
+        <v>-0.3577</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4758</v>
+        <v>-0.3356</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5192</v>
+        <v>-0.0221</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4959</v>
+        <v>2.2149</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4959</v>
+        <v>1.8279</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>0.3869</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6106</v>
+        <v>2.9883</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4505</v>
+        <v>-0.1272</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0611</v>
+        <v>3.1155</v>
       </c>
       <c r="G5" t="n">
         <v>1.7537</v>
@@ -844,13 +844,13 @@
         <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.038</v>
+        <v>0.3398</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2337</v>
+        <v>0.0895</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1958</v>
+        <v>0.2502</v>
       </c>
       <c r="V5" t="n">
         <v>-0.2772</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4317</v>
+        <v>0.4844</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8809</v>
+        <v>1.0425</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4492</v>
+        <v>-0.5581</v>
       </c>
       <c r="G6" t="n">
         <v>0.2623</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1695</v>
+        <v>0.2222</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0605</v>
+        <v>0.1011</v>
       </c>
       <c r="U6" t="n">
-        <v>0.23</v>
+        <v>0.121</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8279</v>
+        <v>0.211</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8787</v>
+        <v>0.0512</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0508</v>
+        <v>0.1598</v>
       </c>
       <c r="G7" t="n">
         <v>0.0155</v>
@@ -1000,13 +1000,13 @@
         <v>1.3674</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9922</v>
+        <v>0.0467</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.1432</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2054</v>
+        <v>-0.0964</v>
       </c>
       <c r="V7" t="n">
         <v>-1.2186</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0619</v>
+        <v>-0.3924</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8803</v>
+        <v>-0.456</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1816</v>
+        <v>0.0636</v>
       </c>
       <c r="G8" t="n">
         <v>0.5933</v>
@@ -1078,13 +1078,13 @@
         <v>2.1488</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.8505</v>
+        <v>-1.181</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0289</v>
+        <v>-0.6045</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.8217</v>
+        <v>-0.5765</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.5726</v>
+        <v>-2.7289</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7248</v>
+        <v>-3.0156</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8478</v>
+        <v>0.2866</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.2969</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0284</v>
+        <v>-2.8049</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2685</v>
+        <v>2.0896</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1841</v>
+        <v>-0.8299</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2651</v>
+        <v>-2.2462</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0809</v>
+        <v>1.4163</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1127</v>
+        <v>0.1146</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7634</v>
+        <v>-0.5587</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.3494</v>
+        <v>0.6733</v>
       </c>
       <c r="P9" t="n">
-        <v>0.586</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
         <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.471</v>
+        <v>0.2951</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1732</v>
+        <v>0.4672</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2978</v>
+        <v>-0.1721</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6093</v>
+        <v>-0.9414</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6093</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.6052</v>
+        <v>-2.8444</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4288</v>
+        <v>-1.8059</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1764</v>
+        <v>-1.0385</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.7151999999999999</v>
+        <v>-3.2969</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.8049</v>
+        <v>-2.0284</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0896</v>
+        <v>-1.2685</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8299</v>
+        <v>-1.1841</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2462</v>
+        <v>-1.2651</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4163</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1146</v>
+        <v>-2.1127</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5587</v>
+        <v>-0.7634</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6733</v>
+        <v>-1.3494</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4189</v>
+        <v>-0.7429</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0539</v>
+        <v>-0.2544</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6351</v>
+        <v>-0.4885</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9414</v>
+        <v>0.6093</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2772</v>
+        <v>0.6093</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8765</v>
+        <v>-4.4249</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8572</v>
+        <v>-3.4328</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0193</v>
+        <v>-0.9921</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6949</v>
@@ -1312,13 +1312,13 @@
         <v>1.9534</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4235</v>
+        <v>-0.9719</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9684</v>
+        <v>-0.544</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4552</v>
+        <v>-0.4279</v>
       </c>
       <c r="V11" t="n">
         <v>1.2186</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.606200000000001</v>
+        <v>8.816700000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7246999999999999</v>
+        <v>1.935</v>
       </c>
       <c r="F12" t="n">
-        <v>6.881500000000001</v>
+        <v>6.881600000000001</v>
       </c>
       <c r="G12" t="n">
-        <v>3.0679</v>
+        <v>3.067900000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.3957</v>
+        <v>2.395699999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6721000000000004</v>
+        <v>0.6720999999999999</v>
       </c>
       <c r="J12" t="n">
         <v>8.313599999999999</v>
@@ -1390,19 +1390,19 @@
         <v>15.6274</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3248</v>
+        <v>-1.1144</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4296</v>
+        <v>-0.2191</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8955000000000002</v>
+        <v>-0.8954000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>3.9332</v>
       </c>
       <c r="W12" t="n">
-        <v>6.537799999999999</v>
+        <v>6.537800000000001</v>
       </c>
       <c r="X12" t="n">
         <v>-2.6048</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1106</v>
+        <v>4.8345</v>
       </c>
       <c r="E13" t="n">
-        <v>4.153</v>
+        <v>3.8496</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9576</v>
+        <v>0.9848</v>
       </c>
       <c r="G13" t="n">
         <v>3.2325</v>
@@ -1468,13 +1468,13 @@
         <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>0.706</v>
+        <v>0.4299</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2918</v>
+        <v>-0.0116</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4143</v>
+        <v>0.4415</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0378</v>
+        <v>1.5788</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6043</v>
+        <v>1.1999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4335</v>
+        <v>0.379</v>
       </c>
       <c r="G14" t="n">
         <v>2.0091</v>
@@ -1546,13 +1546,13 @@
         <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2706</v>
+        <v>0.8116</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0264</v>
+        <v>0.6219</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2442</v>
+        <v>0.1897</v>
       </c>
       <c r="V14" t="n">
         <v>-1.8279</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.4471</v>
+        <v>1.1632</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7527</v>
+        <v>1.5504</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3055</v>
+        <v>-0.3873</v>
       </c>
       <c r="G15" t="n">
         <v>2.3433</v>
@@ -1624,13 +1624,13 @@
         <v>0.9767</v>
       </c>
       <c r="S15" t="n">
-        <v>0.5178</v>
+        <v>0.2338</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2918</v>
+        <v>0.0895</v>
       </c>
       <c r="U15" t="n">
-        <v>0.226</v>
+        <v>0.1443</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2186</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. GUARDIOLA DISPES</t>
+          <t>M. CAPELL OLLER</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.5256</v>
+        <v>0.0703</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.4548</v>
+        <v>0.4426</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9292</v>
+        <v>-0.3723</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.7709</v>
+        <v>-2.4963</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1376</v>
+        <v>0.1732</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6332</v>
+        <v>-2.6696</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.2019</v>
+        <v>-0.6439</v>
       </c>
       <c r="K16" t="n">
-        <v>0.1049</v>
+        <v>1.3507</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3067</v>
+        <v>-1.9947</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.569</v>
+        <v>-1.8524</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.2425</v>
+        <v>-1.1775</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6735</v>
+        <v>-0.6749000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8546</v>
+        <v>-0.7339</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9191</v>
+        <v>-0.4559</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0645</v>
+        <v>-0.278</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.7145</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CAPELL OLLER</t>
+          <t>M. SERRAT PONCE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5599</v>
+        <v>-0.2042</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1393</v>
+        <v>-0.9472</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0.743</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4963</v>
+        <v>-1.1856</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1732</v>
+        <v>-1.2267</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.6696</v>
+        <v>0.0411</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.6439</v>
+        <v>-0.0071</v>
       </c>
       <c r="K17" t="n">
-        <v>1.3507</v>
+        <v>-0.5884</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.9947</v>
+        <v>0.5813</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8524</v>
+        <v>-1.1785</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.1775</v>
+        <v>-0.6382</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6749000000000001</v>
+        <v>-0.5403</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.3641</v>
+        <v>0.5592</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7592</v>
+        <v>0.0366</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6048</v>
+        <v>0.5226</v>
       </c>
       <c r="V17" t="n">
-        <v>2.7145</v>
+        <v>-0.5545</v>
       </c>
       <c r="W17" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MATEU SERRA</t>
+          <t>R. GUARDIOLA DISPES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7018</v>
+        <v>-0.5293</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0792</v>
+        <v>-1.7582</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3774</v>
+        <v>1.2288</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7286</v>
+        <v>-1.7709</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0786</v>
+        <v>-1.1376</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.8071</v>
+        <v>-0.6332</v>
       </c>
       <c r="J18" t="n">
-        <v>0.37</v>
+        <v>-1.2019</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6373</v>
+        <v>0.1049</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2673</v>
+        <v>-1.3067</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0986</v>
+        <v>-0.569</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5587</v>
+        <v>-1.2425</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5399</v>
+        <v>0.6735</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
         <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1402</v>
+        <v>0.8509</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.773</v>
+        <v>0.6158</v>
       </c>
       <c r="U18" t="n">
-        <v>0.9133</v>
+        <v>0.2351</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. SERRAT PONCE</t>
+          <t>M. MATEU SERRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.912</v>
+        <v>-0.9431</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.655</v>
+        <v>-1.7759</v>
       </c>
       <c r="F19" t="n">
-        <v>0.743</v>
+        <v>0.8327</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1856</v>
+        <v>-0.7286</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2267</v>
+        <v>1.0786</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0411</v>
+        <v>-1.8071</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0071</v>
+        <v>0.37</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5884</v>
+        <v>1.6373</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5813</v>
+        <v>-1.2673</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1785</v>
+        <v>-1.0986</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6382</v>
+        <v>-0.5587</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5403</v>
+        <v>-0.5399</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1486</v>
+        <v>-0.1011</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6712</v>
+        <v>-0.4697</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5226</v>
+        <v>0.3686</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.6901</v>
+        <v>-3.9196</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.0766</v>
+        <v>-3.2788</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6135</v>
+        <v>-0.6408</v>
       </c>
       <c r="G20" t="n">
         <v>-1.1463</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3863</v>
+        <v>0.1568</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4458</v>
+        <v>0.2436</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0595</v>
+        <v>-0.0867</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. VANCEA</t>
+          <t>J. CALLAVE FERRER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.8464</v>
+        <v>-4.472</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4051</v>
+        <v>-2.5568</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4413</v>
+        <v>-1.9153</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4741</v>
+        <v>-2.851</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6202</v>
+        <v>-3.0131</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1461</v>
+        <v>0.1621</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6245000000000001</v>
+        <v>-1.3525</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-2.5941</v>
       </c>
       <c r="L21" t="n">
-        <v>1.4163</v>
+        <v>1.2416</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0986</v>
+        <v>-1.4986</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.8283</v>
+        <v>-0.419</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2702</v>
+        <v>-1.0795</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.1022</v>
+        <v>-1.1721</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8584000000000001</v>
+        <v>-0.4024</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4596</v>
+        <v>-0.0322</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3988</v>
+        <v>-0.3701</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1052</v>
+        <v>-1.2186</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7182</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. CALLAVE FERRER</t>
+          <t>M. VANCEA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.966</v>
+        <v>-5.1848</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.8601</v>
+        <v>-3.6073</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1059</v>
+        <v>-1.5775</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.851</v>
+        <v>-0.4741</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.0131</v>
+        <v>-1.6202</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1621</v>
+        <v>1.1461</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3525</v>
+        <v>0.6245000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.5941</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>1.2416</v>
+        <v>1.4163</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.4986</v>
+        <v>-1.0986</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.419</v>
+        <v>-0.8283</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.0795</v>
+        <v>-0.2702</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-3.1255</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>-4.1022</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8964</v>
+        <v>0.52</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3356</v>
+        <v>0.2573</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5608</v>
+        <v>0.2626</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>-2.1052</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>-1.7182</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.606299999999999</v>
+        <v>-7.6062</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.881500000000001</v>
+        <v>-6.8817</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7246000000000001</v>
+        <v>-0.7248999999999999</v>
       </c>
       <c r="G23" t="n">
         <v>-3.067900000000001</v>
@@ -2218,22 +2218,22 @@
         <v>-2.3958</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.672</v>
+        <v>-0.6719999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>5.2457</v>
+        <v>5.245699999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>3.8897</v>
+        <v>3.889700000000001</v>
       </c>
       <c r="L23" t="n">
         <v>1.3561</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.313600000000001</v>
+        <v>-8.313599999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-6.2853</v>
+        <v>-6.285299999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-2.0282</v>
@@ -2251,7 +2251,7 @@
         <v>2.3248</v>
       </c>
       <c r="T23" t="n">
-        <v>0.8955000000000001</v>
+        <v>0.8953</v>
       </c>
       <c r="U23" t="n">
         <v>1.4296</v>
@@ -2263,7 +2263,7 @@
         <v>2.6048</v>
       </c>
       <c r="X23" t="n">
-        <v>-6.537800000000001</v>
+        <v>-6.537799999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484282_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484282_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X23"/>
+  <dimension ref="A1:Y23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.3869</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.4959</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-2.6048</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5545</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.7182</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484282_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,7 @@
       <c r="X23" t="n">
         <v>-6.537799999999999</v>
       </c>
+      <c r="Y23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
